--- a/base_prov/ml/ml_abbott_2026-07-21.xlsx
+++ b/base_prov/ml/ml_abbott_2026-07-21.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\como se me cante\retail-chatbot-main\eci_abbott-main\base_prov\ml\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8A34E10-A49B-4BA3-A740-DF295C273B7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F7F2AC-4428-4286-ABD1-1AB492E71795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -455,9 +455,6 @@
     <t>https://www.mercadolibre.com.mx/pack-x24-formula-especializada-10-a-15-anos-528-l-pediasure-vainilla/p/MLM53398238?pdp_filters=shipping%3Afulfillment%7Cdeal%3AMLM1020488-1#polycard_client=search-desktop&amp;be_origin=backend&amp;search_layout=grid&amp;position=1&amp;type=product&amp;tracking_id=09338827-245d-4257-8235-5b5ce3ab735b&amp;wid=MLM3924762420&amp;sid=search</t>
   </si>
   <si>
-    <t>2026-07-20</t>
-  </si>
-  <si>
     <t>https://www.mercadolibre.com.mx/formula-infantil-con-hierro-similac-etapa-1-350-gramos-na/p/MLM30049354#polycard_client=search-desktop&amp;be_origin=backend&amp;search_layout=grid&amp;position=24&amp;type=product&amp;tracking_id=309d8420-669d-41fa-940b-a23480c9ab43&amp;wid=MLM2004360423&amp;sid=search</t>
   </si>
   <si>
@@ -471,6 +468,9 @@
   </si>
   <si>
     <t>https://www.mercadolibre.com.mx/pedialyte-12-pack-sabor-coco-30-meq/p/MLM67737065?pdp_filters=item_id:MLM5164338894#is_advertising=true&amp;searchVariation=MLM67737065&amp;backend_model=search-backend&amp;be_origin=backend&amp;position=19&amp;search_layout=grid&amp;type=pad&amp;tracking_id=91ad6538-5cb7-4051-afff-8f1c455b883c&amp;ad_domain=VQCATCORE_LST&amp;ad_position=19&amp;ad_click_id=MWU2OWU1ZjMtODgzMy00ZWEzLTljNTQtOWM4ZDg0ZmUyMzA1</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
   </si>
 </sst>
 </file>
@@ -900,7 +900,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
@@ -947,7 +947,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -1135,7 +1135,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -1182,7 +1182,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -1276,7 +1276,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -1323,7 +1323,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B13" t="s">
         <v>13</v>
@@ -1464,7 +1464,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -1511,7 +1511,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -1558,7 +1558,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B16" t="s">
         <v>13</v>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -1699,7 +1699,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -1793,7 +1793,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -1840,7 +1840,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -1887,7 +1887,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -1934,7 +1934,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -1981,7 +1981,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -2075,7 +2075,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -2122,7 +2122,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -2169,7 +2169,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -2208,7 +2208,7 @@
         <v>606</v>
       </c>
       <c r="N29" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="O29" t="s">
         <v>9</v>
@@ -2216,7 +2216,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -2263,7 +2263,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -2310,7 +2310,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -2357,7 +2357,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -2451,7 +2451,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -2498,7 +2498,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -2545,7 +2545,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -2592,7 +2592,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -2639,7 +2639,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -2686,7 +2686,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -2733,7 +2733,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -2772,7 +2772,7 @@
         <v>141</v>
       </c>
       <c r="N41" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O41" t="s">
         <v>9</v>
@@ -2780,7 +2780,7 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -2819,7 +2819,7 @@
         <v>141</v>
       </c>
       <c r="N42" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O42" t="s">
         <v>9</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -2874,7 +2874,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -2913,7 +2913,7 @@
         <v>141</v>
       </c>
       <c r="N44" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O44" t="s">
         <v>9</v>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -2968,7 +2968,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -3007,7 +3007,7 @@
         <v>141</v>
       </c>
       <c r="N46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O46" t="s">
         <v>9</v>
@@ -3015,7 +3015,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -3109,7 +3109,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -3156,7 +3156,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -3203,7 +3203,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -3250,7 +3250,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -3297,7 +3297,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -3344,7 +3344,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -3438,7 +3438,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -3485,7 +3485,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -3532,7 +3532,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -3626,7 +3626,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -3673,7 +3673,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -3767,7 +3767,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -3814,7 +3814,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -3861,7 +3861,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -3908,7 +3908,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -3955,7 +3955,7 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -4002,7 +4002,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -4049,7 +4049,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B69" t="s">
         <v>13</v>
@@ -4096,7 +4096,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -4190,7 +4190,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -4237,7 +4237,7 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -4284,7 +4284,7 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -4331,7 +4331,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -4425,7 +4425,7 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -4472,7 +4472,7 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -4566,7 +4566,7 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
